--- a/03 Content and Social/jackman-ambassador-prospects-ig-2026-09-16-v1.xlsx
+++ b/03 Content and Social/jackman-ambassador-prospects-ig-2026-09-16-v1.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30520"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_FEE6328748632434EF36BED44352EF12600E721E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E858CA62-7EF5-433B-A2C0-36BBA3BA92CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{7BA0058C-5DD6-4F87-A0CA-0D85E6C9BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to Use" sheetId="1" r:id="rId1"/>
@@ -13,9 +13,11 @@
     <sheet name="Scoring Model" sheetId="3" r:id="rId3"/>
     <sheet name="Shop and Dealer Leads" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="409">
   <si>
     <t>Jackman Wheels - Instagram Ambassador Prospects</t>
   </si>
@@ -184,6 +186,9 @@
     <t>Vehicle / Platform</t>
   </si>
   <si>
+    <t>Wheels</t>
+  </si>
+  <si>
     <t>Content Type</t>
   </si>
   <si>
@@ -226,6 +231,9 @@
     <t>Toyota (shoots for others)</t>
   </si>
   <si>
+    <t>Raceline</t>
+  </si>
+  <si>
     <t>Photographer</t>
   </si>
   <si>
@@ -256,6 +264,9 @@
     <t>2017 4Runner TRD Pro + 2025 Lexus GX550 Overtrail</t>
   </si>
   <si>
+    <t>Rays</t>
+  </si>
+  <si>
     <t>Builds / overland</t>
   </si>
   <si>
@@ -268,6 +279,9 @@
     <t>Two rigs = two fitments off one relationship. Already on brand teams, knows how deliverables work.</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>22protaco</t>
   </si>
   <si>
@@ -283,6 +297,9 @@
     <t>Toyota Tacoma TRD Pro</t>
   </si>
   <si>
+    <t>Lock Offroad</t>
+  </si>
+  <si>
     <t>Truck build / desert</t>
   </si>
   <si>
@@ -292,6 +309,9 @@
     <t>Only 56 posts for 12.8K followers - unusually high signal per post. Already shoots wheel close-ups.</t>
   </si>
   <si>
+    <t xml:space="preserve">Does not have a specific deal with LOCK Wheels. </t>
+  </si>
+  <si>
     <t>keepitdirty_offroad</t>
   </si>
   <si>
@@ -304,6 +324,9 @@
     <t>2014 Ford Raptor</t>
   </si>
   <si>
+    <t>Method</t>
+  </si>
+  <si>
     <t>DIY / reviews / group runs</t>
   </si>
   <si>
@@ -388,6 +411,9 @@
     <t>Toyota 4Runner</t>
   </si>
   <si>
+    <t>Reika</t>
+  </si>
+  <si>
     <t>Truck build</t>
   </si>
   <si>
@@ -409,6 +435,9 @@
     <t>Raptor R; Bronco Raptor; Porsche GT3 RS; Alpina XB7</t>
   </si>
   <si>
+    <t>Innov8</t>
+  </si>
+  <si>
     <t>Performance / luxury</t>
   </si>
   <si>
@@ -433,6 +462,9 @@
     <t>2024 Toyota Tacoma</t>
   </si>
   <si>
+    <t>Stealth</t>
+  </si>
+  <si>
     <t>Overland / camping / fishing</t>
   </si>
   <si>
@@ -454,6 +486,9 @@
     <t>Toyota Land Cruiser LC250</t>
   </si>
   <si>
+    <t>Black Rhino</t>
+  </si>
+  <si>
     <t>Overland / family / photography</t>
   </si>
   <si>
@@ -466,6 +501,9 @@
     <t>Bio says DM for content - he already sells content services, so pricing will be a real conversation. LC250 is a fresh platform.</t>
   </si>
   <si>
+    <t xml:space="preserve">Can't make ORE. Willing to work after the show. </t>
+  </si>
+  <si>
     <t>zr2chris22</t>
   </si>
   <si>
@@ -478,6 +516,9 @@
     <t>2022 Chevy Silverado ZR2</t>
   </si>
   <si>
+    <t>KMC</t>
+  </si>
+  <si>
     <t>Off-road / builds</t>
   </si>
   <si>
@@ -499,6 +540,9 @@
     <t>2021 4Runner TRD Pro, solid axle swap</t>
   </si>
   <si>
+    <t>Beadlocks</t>
+  </si>
+  <si>
     <t>Builds / reels</t>
   </si>
   <si>
@@ -547,6 +591,9 @@
     <t>Media production team</t>
   </si>
   <si>
+    <t>DV8</t>
+  </si>
+  <si>
     <t>Photo / video production</t>
   </si>
   <si>
@@ -1214,48 +1261,6 @@
   </si>
   <si>
     <t>Source: public Instagram profiles, read 2026-09-16.</t>
-  </si>
-  <si>
-    <t>Wheels</t>
-  </si>
-  <si>
-    <t>Rays</t>
-  </si>
-  <si>
-    <t>Lock Offroad</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Black Rhino</t>
-  </si>
-  <si>
-    <t>DV8</t>
-  </si>
-  <si>
-    <t>KMC</t>
-  </si>
-  <si>
-    <t>Beadlocks</t>
-  </si>
-  <si>
-    <t>Stealth</t>
-  </si>
-  <si>
-    <t>Innov8</t>
-  </si>
-  <si>
-    <t>Reika</t>
-  </si>
-  <si>
-    <t>Raceline</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">He needs to follow us back to DM </t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1270,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1336,6 +1341,14 @@
       <sz val="12"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1385,10 +1398,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1426,24 +1440,18 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1457,10 +1465,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1786,99 +1790,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="116" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
         <v>17</v>
       </c>
@@ -1889,7 +1893,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
         <v>20</v>
       </c>
@@ -1900,82 +1904,82 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1">
       <c r="A42" s="4" t="s">
         <v>38</v>
       </c>
@@ -1989,7 +1993,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2009,7 +2013,7 @@
     <col min="24" max="24" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="25.5">
       <c r="A1" s="7" t="s">
         <v>39</v>
       </c>
@@ -2044,34 +2048,34 @@
         <v>49</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>394</v>
+        <v>50</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>17</v>
@@ -2083,7 +2087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="57.95" customHeight="1">
       <c r="A2" s="8" t="str">
         <f t="shared" ref="A2:A37" si="0">IF(B2&gt;=75,"A - contact first",IF(B2&gt;=55,"B - second wave",IF(B2&gt;=35,"C - watchlist","D - not now")))</f>
         <v>A - contact first</v>
@@ -2093,13 +2097,13 @@
         <v>100</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="8" t="s">
         <v>61</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>62</v>
       </c>
       <c r="F2" s="10">
         <v>13400</v>
@@ -2115,19 +2119,19 @@
         <v>45.117845117845121</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>405</v>
+        <v>65</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O2" s="8">
         <v>1</v>
@@ -2142,92 +2146,92 @@
         <v>0</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U2" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="V2" s="12"/>
       <c r="W2" s="12"/>
       <c r="X2" s="12"/>
     </row>
-    <row r="3" spans="1:24" s="26" customFormat="1" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="str">
+    <row r="3" spans="1:24" ht="57.95" customHeight="1">
+      <c r="A3" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="9">
         <f>ROUND('Scoring Model'!$B$4*IF(AND(F3&gt;='Scoring Model'!$B$11,F3&lt;='Scoring Model'!$B$12),1,IF(F3&gt;'Scoring Model'!$B$12,'Scoring Model'!$B$13,'Scoring Model'!$B$14))+'Scoring Model'!$B$5*IF(I3&gt;=20,1,IF(I3&gt;=10,0.8,IF(I3&gt;=5,0.6,IF(I3&gt;=2,0.4,0.15))))+'Scoring Model'!$B$6*O3+'Scoring Model'!$B$7*P3+'Scoring Model'!$B$8*Q3-'Scoring Model'!$B$9*R3,1)</f>
         <v>97</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="22" t="s">
+      <c r="C3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="24">
+      <c r="D3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="10">
         <v>20700</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="10">
         <v>1307</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="10">
         <v>508</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="9">
         <f t="shared" si="1"/>
         <v>15.83779648048967</v>
       </c>
-      <c r="J3" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="25" t="s">
-        <v>395</v>
-      </c>
-      <c r="M3" s="25" t="s">
+      <c r="J3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="K3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="22">
-        <v>1</v>
-      </c>
-      <c r="P3" s="22">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="22">
-        <v>1</v>
-      </c>
-      <c r="R3" s="22">
-        <v>0</v>
-      </c>
-      <c r="S3" s="22" t="s">
+      <c r="L3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="T3" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="U3" s="25" t="s">
+      <c r="M3" s="11" t="s">
         <v>77</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O3" s="8">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8">
+        <v>0</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="V3" s="20"/>
       <c r="W3" s="20" t="s">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="X3" s="20"/>
     </row>
-    <row r="4" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="57.95" customHeight="1">
       <c r="A4" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2237,13 +2241,13 @@
         <v>85</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F4" s="10">
         <v>12800</v>
@@ -2259,48 +2263,50 @@
         <v>32.904884318766065</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="O4" s="8">
+        <v>1</v>
+      </c>
+      <c r="P4" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="V4" s="12"/>
+      <c r="W4" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="K4" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="O4" s="8">
-        <v>1</v>
-      </c>
-      <c r="P4" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="V4" s="12"/>
-      <c r="W4" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="X4" s="12"/>
-    </row>
-    <row r="5" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X4" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="57.95" customHeight="1">
       <c r="A5" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2310,13 +2316,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F5" s="10">
         <v>19900</v>
@@ -2332,19 +2338,19 @@
         <v>27.29766803840878</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>397</v>
+        <v>96</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="O5" s="8">
         <v>1</v>
@@ -2359,19 +2365,19 @@
         <v>0</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="V5" s="12"/>
       <c r="W5" s="12"/>
       <c r="X5" s="12"/>
     </row>
-    <row r="6" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="57.95" customHeight="1">
       <c r="A6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2381,13 +2387,13 @@
         <v>85</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F6" s="10">
         <v>11900</v>
@@ -2403,19 +2409,19 @@
         <v>28.26603325415677</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>397</v>
+        <v>96</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O6" s="8">
         <v>1</v>
@@ -2430,19 +2436,19 @@
         <v>0</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
     </row>
-    <row r="7" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="57.95" customHeight="1">
       <c r="A7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2452,13 +2458,13 @@
         <v>85</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F7" s="10">
         <v>34800</v>
@@ -2474,19 +2480,19 @@
         <v>41.82692307692308</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>396</v>
+        <v>87</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="O7" s="8">
         <v>1</v>
@@ -2501,19 +2507,21 @@
         <v>0</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
+      <c r="W7" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="X7" s="12"/>
     </row>
-    <row r="8" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="57.95" customHeight="1">
       <c r="A8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2523,13 +2531,13 @@
         <v>80</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F8" s="10">
         <v>23800</v>
@@ -2545,19 +2553,19 @@
         <v>21.69553327256153</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>404</v>
+        <v>125</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O8" s="8">
         <v>0</v>
@@ -2572,19 +2580,19 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="12"/>
     </row>
-    <row r="9" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="57.95" customHeight="1">
       <c r="A9" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2594,13 +2602,13 @@
         <v>80</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F9" s="10">
         <v>14900</v>
@@ -2616,19 +2624,19 @@
         <v>27.592592592592592</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>403</v>
+        <v>133</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="O9" s="8">
         <v>0</v>
@@ -2643,165 +2651,167 @@
         <v>0</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="U9" s="11" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
     </row>
-    <row r="10" spans="1:24" s="26" customFormat="1" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="str">
+    <row r="10" spans="1:24" ht="57.95" customHeight="1">
+      <c r="A10" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="9">
         <f>ROUND('Scoring Model'!$B$4*IF(AND(F10&gt;='Scoring Model'!$B$11,F10&lt;='Scoring Model'!$B$12),1,IF(F10&gt;'Scoring Model'!$B$12,'Scoring Model'!$B$13,'Scoring Model'!$B$14))+'Scoring Model'!$B$5*IF(I10&gt;=20,1,IF(I10&gt;=10,0.8,IF(I10&gt;=5,0.6,IF(I10&gt;=2,0.4,0.15))))+'Scoring Model'!$B$6*O10+'Scoring Model'!$B$7*P10+'Scoring Model'!$B$8*Q10-'Scoring Model'!$B$9*R10,1)</f>
         <v>79</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" s="24">
+      <c r="C10" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" s="10">
         <v>13600</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="10">
         <v>1857</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="10">
         <v>431</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="9">
         <f t="shared" si="1"/>
         <v>7.3236402800215403</v>
       </c>
-      <c r="J10" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>402</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="N10" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="O10" s="22">
-        <v>1</v>
-      </c>
-      <c r="P10" s="22">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="22">
-        <v>0</v>
-      </c>
-      <c r="R10" s="22">
-        <v>0</v>
-      </c>
-      <c r="S10" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="T10" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="U10" s="25" t="s">
-        <v>135</v>
+      <c r="J10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="8">
+        <v>1</v>
+      </c>
+      <c r="P10" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="T10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="V10" s="20"/>
       <c r="W10" s="20" t="s">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="X10" s="20"/>
     </row>
-    <row r="11" spans="1:24" s="26" customFormat="1" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="str">
+    <row r="11" spans="1:24" ht="57.95" customHeight="1">
+      <c r="A11" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="9">
         <f>ROUND('Scoring Model'!$B$4*IF(AND(F11&gt;='Scoring Model'!$B$11,F11&lt;='Scoring Model'!$B$12),1,IF(F11&gt;'Scoring Model'!$B$12,'Scoring Model'!$B$13,'Scoring Model'!$B$14))+'Scoring Model'!$B$5*IF(I11&gt;=20,1,IF(I11&gt;=10,0.8,IF(I11&gt;=5,0.6,IF(I11&gt;=2,0.4,0.15))))+'Scoring Model'!$B$6*O11+'Scoring Model'!$B$7*P11+'Scoring Model'!$B$8*Q11-'Scoring Model'!$B$9*R11,1)</f>
         <v>79</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="24">
+      <c r="C11" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="10">
         <v>9628</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="10">
         <v>1604</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="10">
         <v>295</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="9">
         <f t="shared" si="1"/>
         <v>6.0024937655860349</v>
       </c>
-      <c r="J11" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>398</v>
-      </c>
-      <c r="M11" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="N11" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="O11" s="22">
-        <v>1</v>
-      </c>
-      <c r="P11" s="22">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>0</v>
-      </c>
-      <c r="R11" s="22">
-        <v>0</v>
-      </c>
-      <c r="S11" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="T11" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="U11" s="25" t="s">
-        <v>143</v>
+      <c r="J11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="O11" s="8">
+        <v>1</v>
+      </c>
+      <c r="P11" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="T11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>154</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="20" t="s">
-        <v>406</v>
-      </c>
-      <c r="X11" s="20"/>
-    </row>
-    <row r="12" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="X11" s="21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="57.95" customHeight="1">
       <c r="A12" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2811,13 +2821,13 @@
         <v>77</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F12" s="10">
         <v>22400</v>
@@ -2833,20 +2843,20 @@
         <v>14.66928618205632</v>
       </c>
       <c r="J12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="N12" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="K12" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>400</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>109</v>
-      </c>
       <c r="O12" s="8">
         <v>0</v>
       </c>
@@ -2860,19 +2870,19 @@
         <v>0</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
     </row>
-    <row r="13" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="57.95" customHeight="1">
       <c r="A13" s="8" t="str">
         <f t="shared" si="0"/>
         <v>A - contact first</v>
@@ -2882,13 +2892,13 @@
         <v>77</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F13" s="10">
         <v>12400</v>
@@ -2904,19 +2914,19 @@
         <v>16.734143049932523</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>401</v>
+        <v>168</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
@@ -2931,19 +2941,19 @@
         <v>0</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
     </row>
-    <row r="14" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="57.95" customHeight="1">
       <c r="A14" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -2953,13 +2963,13 @@
         <v>74</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="F14" s="10">
         <v>12100</v>
@@ -2975,19 +2985,19 @@
         <v>9.1389728096676741</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="O14" s="8">
         <v>0</v>
@@ -3002,19 +3012,19 @@
         <v>0</v>
       </c>
       <c r="S14" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
     </row>
-    <row r="15" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="57.95" customHeight="1">
       <c r="A15" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3024,13 +3034,13 @@
         <v>74</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F15" s="10">
         <v>11500</v>
@@ -3046,19 +3056,19 @@
         <v>7.2555205047318614</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>399</v>
+        <v>185</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="O15" s="8">
         <v>0</v>
@@ -3073,19 +3083,19 @@
         <v>0</v>
       </c>
       <c r="S15" s="8" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
       <c r="X15" s="12"/>
     </row>
-    <row r="16" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="57.95" customHeight="1">
       <c r="A16" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3095,13 +3105,13 @@
         <v>71</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F16" s="10">
         <v>8272</v>
@@ -3117,19 +3127,19 @@
         <v>2.8078750848608283</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="O16" s="8">
         <v>0</v>
@@ -3144,19 +3154,19 @@
         <v>0</v>
       </c>
       <c r="S16" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="V16" s="12"/>
       <c r="W16" s="12"/>
       <c r="X16" s="12"/>
     </row>
-    <row r="17" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="57.95" customHeight="1">
       <c r="A17" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3166,13 +3176,13 @@
         <v>65</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F17" s="10">
         <v>18100</v>
@@ -3188,17 +3198,17 @@
         <v>26.308139534883722</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" s="11" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O17" s="8">
         <v>0</v>
@@ -3213,19 +3223,19 @@
         <v>0</v>
       </c>
       <c r="S17" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="V17" s="12"/>
       <c r="W17" s="12"/>
       <c r="X17" s="12"/>
     </row>
-    <row r="18" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="57.95" customHeight="1">
       <c r="A18" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3235,13 +3245,13 @@
         <v>65</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F18" s="10">
         <v>11400</v>
@@ -3257,19 +3267,19 @@
         <v>50</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>396</v>
+        <v>87</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O18" s="8">
         <v>0</v>
@@ -3284,19 +3294,19 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="V18" s="12"/>
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="57.95" customHeight="1">
       <c r="A19" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3306,13 +3316,13 @@
         <v>65</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F19" s="10">
         <v>20200</v>
@@ -3328,17 +3338,17 @@
         <v>20.910973084886127</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="L19" s="11"/>
       <c r="M19" s="11" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O19" s="8">
         <v>0</v>
@@ -3353,19 +3363,19 @@
         <v>0</v>
       </c>
       <c r="S19" s="8" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="V19" s="12"/>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
     </row>
-    <row r="20" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="57.95" customHeight="1">
       <c r="A20" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3375,13 +3385,13 @@
         <v>65</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F20" s="10">
         <v>25600</v>
@@ -3397,17 +3407,17 @@
         <v>90.459363957597176</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="L20" s="11"/>
       <c r="M20" s="11" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="O20" s="8">
         <v>0</v>
@@ -3422,19 +3432,19 @@
         <v>0</v>
       </c>
       <c r="S20" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="V20" s="12"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12"/>
     </row>
-    <row r="21" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="57.95" customHeight="1">
       <c r="A21" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3444,13 +3454,13 @@
         <v>65</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F21" s="10">
         <v>29300</v>
@@ -3466,17 +3476,17 @@
         <v>26.588021778584391</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="L21" s="11"/>
       <c r="M21" s="11" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="O21" s="8">
         <v>0</v>
@@ -3491,19 +3501,19 @@
         <v>0</v>
       </c>
       <c r="S21" s="8" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="V21" s="12"/>
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
     </row>
-    <row r="22" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="57.95" customHeight="1">
       <c r="A22" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3513,13 +3523,13 @@
         <v>65</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="F22" s="10">
         <v>35800</v>
@@ -3535,17 +3545,17 @@
         <v>41.87134502923977</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="L22" s="11"/>
       <c r="M22" s="11" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="O22" s="8">
         <v>0</v>
@@ -3560,19 +3570,19 @@
         <v>0</v>
       </c>
       <c r="S22" s="8" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="T22" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="57.95" customHeight="1">
       <c r="A23" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3582,13 +3592,13 @@
         <v>65</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="F23" s="10">
         <v>43500</v>
@@ -3604,17 +3614,17 @@
         <v>22.492244053774559</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="L23" s="11"/>
       <c r="M23" s="11" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="O23" s="8">
         <v>0</v>
@@ -3629,19 +3639,19 @@
         <v>0</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
       <c r="X23" s="12"/>
     </row>
-    <row r="24" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="57.95" customHeight="1">
       <c r="A24" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3651,13 +3661,13 @@
         <v>62</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="F24" s="10">
         <v>9080</v>
@@ -3673,17 +3683,17 @@
         <v>10.4247990815155</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="L24" s="11"/>
       <c r="M24" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="O24" s="8">
         <v>0</v>
@@ -3698,19 +3708,19 @@
         <v>0</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
       <c r="X24" s="12"/>
     </row>
-    <row r="25" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="57.95" customHeight="1">
       <c r="A25" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3720,13 +3730,13 @@
         <v>62</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="F25" s="10">
         <v>7403</v>
@@ -3742,17 +3752,17 @@
         <v>14.572834645669291</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="L25" s="11"/>
       <c r="M25" s="11" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O25" s="8">
         <v>0</v>
@@ -3767,19 +3777,19 @@
         <v>0</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="V25" s="12"/>
       <c r="W25" s="12"/>
       <c r="X25" s="12"/>
     </row>
-    <row r="26" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="57.95" customHeight="1">
       <c r="A26" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3789,13 +3799,13 @@
         <v>59</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="F26" s="10">
         <v>12800</v>
@@ -3811,17 +3821,17 @@
         <v>9.2219020172910664</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="11" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O26" s="8">
         <v>0</v>
@@ -3836,19 +3846,19 @@
         <v>0</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="V26" s="12"/>
       <c r="W26" s="12"/>
       <c r="X26" s="12"/>
     </row>
-    <row r="27" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="57.95" customHeight="1">
       <c r="A27" s="8" t="str">
         <f t="shared" si="0"/>
         <v>B - second wave</v>
@@ -3858,13 +3868,13 @@
         <v>56</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F27" s="10">
         <v>5474</v>
@@ -3880,17 +3890,17 @@
         <v>2.2279202279202277</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="L27" s="11"/>
       <c r="M27" s="11" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="O27" s="8">
         <v>0</v>
@@ -3905,19 +3915,19 @@
         <v>0</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="V27" s="12"/>
       <c r="W27" s="12"/>
       <c r="X27" s="12"/>
     </row>
-    <row r="28" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="57.95" customHeight="1">
       <c r="A28" s="8" t="str">
         <f t="shared" si="0"/>
         <v>C - watchlist</v>
@@ -3927,13 +3937,13 @@
         <v>50</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="F28" s="10">
         <v>39900</v>
@@ -3949,17 +3959,17 @@
         <v>39.426877470355734</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="L28" s="11"/>
       <c r="M28" s="11" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O28" s="8">
         <v>0</v>
@@ -3974,19 +3984,19 @@
         <v>0</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="T28" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
       <c r="X28" s="12"/>
     </row>
-    <row r="29" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="57.95" customHeight="1">
       <c r="A29" s="8" t="str">
         <f t="shared" si="0"/>
         <v>C - watchlist</v>
@@ -3996,13 +4006,13 @@
         <v>50</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="F29" s="10">
         <v>4558</v>
@@ -4018,17 +4028,17 @@
         <v>6.7726597325408617</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="L29" s="11"/>
       <c r="M29" s="11" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="O29" s="8">
         <v>0</v>
@@ -4043,19 +4053,19 @@
         <v>0</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
       <c r="X29" s="12"/>
     </row>
-    <row r="30" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="57.95" customHeight="1">
       <c r="A30" s="8" t="str">
         <f t="shared" si="0"/>
         <v>C - watchlist</v>
@@ -4065,13 +4075,13 @@
         <v>45</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F30" s="10">
         <v>63100</v>
@@ -4087,17 +4097,17 @@
         <v>31.772406847935549</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" s="11" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="O30" s="8">
         <v>0</v>
@@ -4112,19 +4122,19 @@
         <v>0</v>
       </c>
       <c r="S30" s="8" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="T30" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
     </row>
-    <row r="31" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="57.95" customHeight="1">
       <c r="A31" s="8" t="str">
         <f t="shared" si="0"/>
         <v>C - watchlist</v>
@@ -4134,13 +4144,13 @@
         <v>42</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="F31" s="10">
         <v>6287</v>
@@ -4156,17 +4166,17 @@
         <v>11.907196969696969</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="L31" s="11"/>
       <c r="M31" s="11" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="O31" s="8">
         <v>0</v>
@@ -4181,19 +4191,19 @@
         <v>1</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
     </row>
-    <row r="32" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="57.95" customHeight="1">
       <c r="A32" s="8" t="str">
         <f t="shared" si="0"/>
         <v>C - watchlist</v>
@@ -4203,13 +4213,13 @@
         <v>41</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="F32" s="10">
         <v>4355</v>
@@ -4225,17 +4235,17 @@
         <v>23.288770053475936</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="L32" s="11"/>
       <c r="M32" s="11" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O32" s="8">
         <v>0</v>
@@ -4250,19 +4260,19 @@
         <v>0</v>
       </c>
       <c r="S32" s="8" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="T32" s="8" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="V32" s="12"/>
       <c r="W32" s="12"/>
       <c r="X32" s="12"/>
     </row>
-    <row r="33" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="57.95" customHeight="1">
       <c r="A33" s="8" t="str">
         <f t="shared" si="0"/>
         <v>C - watchlist</v>
@@ -4272,13 +4282,13 @@
         <v>39</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="F33" s="10">
         <v>7841</v>
@@ -4294,17 +4304,17 @@
         <v>7.6274319066147864</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="L33" s="11"/>
       <c r="M33" s="11" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="O33" s="8">
         <v>0</v>
@@ -4319,19 +4329,19 @@
         <v>0</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T33" s="8" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="V33" s="12"/>
       <c r="W33" s="12"/>
       <c r="X33" s="12"/>
     </row>
-    <row r="34" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="57.95" customHeight="1">
       <c r="A34" s="8" t="str">
         <f t="shared" si="0"/>
         <v>C - watchlist</v>
@@ -4341,13 +4351,13 @@
         <v>35</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="F34" s="10">
         <v>2473</v>
@@ -4363,17 +4373,17 @@
         <v>6.5946666666666669</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="L34" s="11"/>
       <c r="M34" s="11" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O34" s="8">
         <v>0</v>
@@ -4388,19 +4398,19 @@
         <v>0</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T34" s="8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="V34" s="12"/>
       <c r="W34" s="12"/>
       <c r="X34" s="12"/>
     </row>
-    <row r="35" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="57.95" customHeight="1">
       <c r="A35" s="8" t="str">
         <f t="shared" si="0"/>
         <v>D - not now</v>
@@ -4410,13 +4420,13 @@
         <v>28.3</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="F35" s="10">
         <v>408</v>
@@ -4432,17 +4442,17 @@
         <v>0.17042606516290726</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="L35" s="11"/>
       <c r="M35" s="11" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O35" s="8">
         <v>1</v>
@@ -4457,19 +4467,19 @@
         <v>0</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="T35" s="8" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="V35" s="12"/>
       <c r="W35" s="12"/>
       <c r="X35" s="12"/>
     </row>
-    <row r="36" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" ht="57.95" customHeight="1">
       <c r="A36" s="8" t="str">
         <f t="shared" si="0"/>
         <v>D - not now</v>
@@ -4479,13 +4489,13 @@
         <v>12</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="F36" s="10">
         <v>4717</v>
@@ -4501,17 +4511,17 @@
         <v>3.7377179080824088</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="L36" s="11"/>
       <c r="M36" s="11" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="O36" s="8">
         <v>0</v>
@@ -4526,19 +4536,19 @@
         <v>0</v>
       </c>
       <c r="S36" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T36" s="8" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="V36" s="12"/>
       <c r="W36" s="12"/>
       <c r="X36" s="12"/>
     </row>
-    <row r="37" spans="1:24" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="57.95" customHeight="1">
       <c r="A37" s="8" t="str">
         <f t="shared" si="0"/>
         <v>D - not now</v>
@@ -4548,13 +4558,13 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="F37" s="10">
         <v>407</v>
@@ -4570,17 +4580,17 @@
         <v>1.3890784982935154</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" s="11" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O37" s="8">
         <v>0</v>
@@ -4595,35 +4605,38 @@
         <v>0</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T37" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="V37" s="12"/>
       <c r="W37" s="12"/>
       <c r="X37" s="12"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24">
       <c r="A39" s="13" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24">
       <c r="A40" s="13" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24">
       <c r="A41" s="13" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X37" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{2135F13C-CC26-45B1-8C93-6BAA3A5309A4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
@@ -4632,155 +4645,155 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16.5">
       <c r="A1" s="14" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="15" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B4" s="6">
         <v>30</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B5" s="6">
         <v>15</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B6" s="6">
         <v>20</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="B7" s="6">
         <v>20</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="B8" s="6">
         <v>15</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="B9" s="6">
         <v>20</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="16" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B11" s="6">
         <v>5000</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="B12" s="6">
         <v>25000</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="B13" s="6">
         <v>0.5</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="B14" s="6">
         <v>0.2</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="17" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="B16" s="17">
         <f>B4+B5+B6+B7+B8</f>
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -4792,7 +4805,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4804,17 +4817,17 @@
     <col min="8" max="8" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75">
       <c r="A1" s="18" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="15" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="19" t="s">
         <v>41</v>
       </c>
@@ -4828,203 +4841,203 @@
         <v>48</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>371</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="13" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
